--- a/Data/Cleaned/Pooled/elem_male_18.xlsx
+++ b/Data/Cleaned/Pooled/elem_male_18.xlsx
@@ -13,15 +13,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>qnt</t>
+    <t>quantile</t>
   </si>
   <si>
-    <t>O</t>
+    <t>year</t>
   </si>
   <si>
-    <t>group</t>
+    <t>employment</t>
+  </si>
+  <si>
+    <t>variable</t>
   </si>
   <si>
     <t>coef</t>
@@ -30,16 +33,10 @@
     <t>se</t>
   </si>
   <si>
-    <t>h</t>
+    <t>t-stat</t>
   </si>
   <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>lb</t>
-  </si>
-  <si>
-    <t>ub</t>
+    <t>p-value</t>
   </si>
 </sst>
 </file>
@@ -110,9 +107,6 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
     </row>
   </sheetData>
 </worksheet>
